--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/DISTRICT_OF_COLUMBIA_2016.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/DISTRICT_OF_COLUMBIA_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C3">
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -472,7 +492,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C8">
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amatenango del Valle</t>
+          <t>Amatenango Del Valle</t>
         </is>
       </c>
       <c r="C9">
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -703,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -745,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -758,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -771,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -784,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -797,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -810,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -823,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -854,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -869,7 +1009,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -885,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Apaxco</t>
@@ -898,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -911,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chapa de Mota</t>
+          <t>Chapa De Mota</t>
         </is>
       </c>
       <c r="C40">
@@ -924,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Chapultepec</t>
@@ -937,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -950,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C43">
@@ -963,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Joquicingo</t>
@@ -976,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C45">
@@ -989,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1002,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Otumba</t>
@@ -1015,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C48">
@@ -1028,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1041,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -1054,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C51">
@@ -1067,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1124,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -1137,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1157,7 +1392,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C58">
@@ -1168,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1181,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C60">
@@ -1194,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -1207,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -1220,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C63">
@@ -1233,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C64">
@@ -1246,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C65">
@@ -1259,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C66">
@@ -1272,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1285,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C68">
@@ -1298,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C69">
@@ -1311,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -1324,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1337,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1350,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -1363,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C74">
@@ -1376,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C75">
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Zitlala</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1446,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C80">
@@ -1459,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>San Salvador</t>
@@ -1472,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C82">
@@ -1485,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1516,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1529,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C86">
@@ -1542,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C87">
@@ -1555,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -1568,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1581,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1612,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -1625,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -1638,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1651,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1664,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1677,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1708,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -1721,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1734,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -1747,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -1760,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1773,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1804,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1835,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C108">
@@ -1848,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Concepción Pápalo</t>
@@ -1861,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eloxochitlán de Flores Magón</t>
+          <t>Eloxochitlán De Flores Magón</t>
         </is>
       </c>
       <c r="C110">
@@ -1874,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C111">
@@ -1887,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C112">
@@ -1900,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C113">
@@ -1913,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -1926,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>San Carlos Yautepec</t>
@@ -1939,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>San Juan Chicomezúchil</t>
@@ -1952,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -1965,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>San Juan Ozolotepec</t>
@@ -1978,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -1991,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -2004,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -2017,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -2030,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Santiago Tapextla</t>
@@ -2043,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Santiago Yolomécatl</t>
@@ -2056,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Santo Tomás Mazaltepec</t>
@@ -2069,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Heroica Villa Tezoatlán de Segura y Luna, Cuna de la Independencia de Oaxaca</t>
+          <t>Heroica Villa Tezoatlán De Segura Y Luna, Cuna De La Independencia De Oaxaca</t>
         </is>
       </c>
       <c r="C126">
@@ -2082,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C127">
@@ -2095,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2126,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Chalchicomula de Sesma</t>
+          <t>Chalchicomula De Sesma</t>
         </is>
       </c>
       <c r="C130">
@@ -2139,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -2152,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Huehuetlán el Grande</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C132">
@@ -2165,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Ixcaquixtla</t>
@@ -2178,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C134">
@@ -2191,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Molcaxac</t>
@@ -2204,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Ocoyucan</t>
@@ -2217,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2230,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -2243,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -2256,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -2269,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C141">
@@ -2282,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Soltepec</t>
@@ -2295,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -2308,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tecomatlán</t>
@@ -2321,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2334,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -2347,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C147">
@@ -2360,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -2373,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C149">
@@ -2386,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Xochitlán Todos Santos</t>
@@ -2399,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2430,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2450,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C154">
@@ -2461,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2492,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Tacotalpa</t>
@@ -2505,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2525,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Soto la Marina</t>
+          <t>Soto La Marina</t>
         </is>
       </c>
       <c r="C159">
@@ -2536,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2567,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -2580,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -2593,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -2606,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Tocatlán</t>
@@ -2619,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2639,7 +3354,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C167">
@@ -2650,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2663,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -2676,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Las Vigas de Ramírez</t>
+          <t>Las Vigas De Ramírez</t>
         </is>
       </c>
       <c r="C170">
@@ -2689,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Maltrata</t>
@@ -2702,9 +3437,14 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C172">
@@ -2715,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -2728,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -2741,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2754,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2767,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2780,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -2793,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -2806,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2837,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2860,76 +3645,6 @@
       </c>
       <c r="D183">
         <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
